--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_INELTRON SANTO DOMINGO BETANZOS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_INELTRON SANTO DOMINGO BETANZOS.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>74.71120000000001</v>
+        <v>88.36320000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>86.46249999999999</v>
+        <v>101.9673</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.7509</v>
+        <v>-13.6042</v>
       </c>
       <c r="G2" t="n">
         <v>60.19</v>
@@ -610,13 +610,13 @@
         <v>68.9384</v>
       </c>
       <c r="S2" t="n">
-        <v>-13.4663</v>
+        <v>0.1855</v>
       </c>
       <c r="T2" t="n">
-        <v>-13.6509</v>
+        <v>1.854</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1849000000000002</v>
+        <v>-1.6685</v>
       </c>
       <c r="V2" t="n">
         <v>42.0886</v>
@@ -643,13 +643,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>41.455</v>
+        <v>23.9938</v>
       </c>
       <c r="E3" t="n">
-        <v>55.8973</v>
+        <v>36.9619</v>
       </c>
       <c r="F3" t="n">
-        <v>-14.4423</v>
+        <v>-12.9678</v>
       </c>
       <c r="G3" t="n">
         <v>8.507999999999999</v>
@@ -688,13 +688,13 @@
         <v>43.2822</v>
       </c>
       <c r="S3" t="n">
-        <v>32.2863</v>
+        <v>14.8254</v>
       </c>
       <c r="T3" t="n">
-        <v>34.3625</v>
+        <v>15.4271</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.0759</v>
+        <v>-0.6018000000000002</v>
       </c>
       <c r="V3" t="n">
         <v>17.5036</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>M. AGRASO VARELA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>8.319099999999999</v>
+        <v>-1.1288</v>
       </c>
       <c r="E4" t="n">
-        <v>10.1751</v>
+        <v>-1.4114</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8561</v>
+        <v>0.2826000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-8.4641</v>
+        <v>-0.222</v>
       </c>
       <c r="H4" t="n">
-        <v>11.1087</v>
+        <v>-0.3685</v>
       </c>
       <c r="I4" t="n">
-        <v>-19.5733</v>
+        <v>0.1464</v>
       </c>
       <c r="J4" t="n">
-        <v>43.8156</v>
+        <v>-0.2979999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>35.6933</v>
+        <v>-0.3028</v>
       </c>
       <c r="L4" t="n">
-        <v>8.1221</v>
+        <v>0.0048</v>
       </c>
       <c r="M4" t="n">
-        <v>-52.2801</v>
+        <v>0.07600000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-24.5848</v>
+        <v>-0.06569999999999998</v>
       </c>
       <c r="O4" t="n">
-        <v>-27.6949</v>
+        <v>0.1415999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>7.6379</v>
+        <v>0.1959</v>
       </c>
       <c r="Q4" t="n">
-        <v>-55.6208</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>63.2591</v>
+        <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>19.1392</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>14.4885</v>
+        <v>-0.1341</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6508</v>
+        <v>-0.4177</v>
       </c>
       <c r="V4" t="n">
-        <v>-9.994199999999999</v>
+        <v>-0.5508</v>
       </c>
       <c r="W4" t="n">
-        <v>7.492699999999999</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-17.4866</v>
+        <v>-0.5508</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. AGRASO VARELA</t>
+          <t>X. FOLCH CLARAMUNT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.574</v>
+        <v>-2.4952</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.616</v>
+        <v>-6.5065</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04210000000000003</v>
+        <v>4.0111</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.222</v>
+        <v>-4.2496</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3685</v>
+        <v>-0.8396</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1464</v>
+        <v>-3.4099</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2979999999999999</v>
+        <v>-0.5651999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3028</v>
+        <v>2.0036</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0048</v>
+        <v>-2.5689</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07600000000000001</v>
+        <v>-3.6845</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06569999999999998</v>
+        <v>-2.8439</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1415999999999999</v>
+        <v>-0.8412000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1959</v>
+        <v>0.7832000000000003</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-9.204699999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1751</v>
+        <v>9.9879</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9971</v>
+        <v>0.7404999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3388</v>
+        <v>2.0466</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6583</v>
+        <v>-1.3061</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5508</v>
+        <v>0.2303000000000003</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5508</v>
+        <v>-0.9862999999999996</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.4431</v>
+        <v>-2.4973</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6232</v>
+        <v>-0.8379000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8198</v>
+        <v>-1.6594</v>
       </c>
       <c r="G6" t="n">
         <v>-1.5165</v>
@@ -922,13 +922,13 @@
         <v>2.9377</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4518</v>
+        <v>-0.5061</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3482</v>
+        <v>0.1335</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-2.4332</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. FOLCH CLARAMUNT</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.966000000000001</v>
+        <v>-2.837800000000002</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.520099999999999</v>
+        <v>3.229499999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5542</v>
+        <v>-6.0675</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.2496</v>
+        <v>-8.4641</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8396</v>
+        <v>11.1087</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.4099</v>
+        <v>-19.5733</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5651999999999999</v>
+        <v>43.8156</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0036</v>
+        <v>35.6933</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.5689</v>
+        <v>8.1221</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.6845</v>
+        <v>-52.2801</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.8439</v>
+        <v>-24.5848</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8412000000000001</v>
+        <v>-27.6949</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7832000000000003</v>
+        <v>7.6379</v>
       </c>
       <c r="Q7" t="n">
-        <v>-9.204699999999999</v>
+        <v>-55.6208</v>
       </c>
       <c r="R7" t="n">
-        <v>9.9879</v>
+        <v>63.2591</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7302000000000002</v>
+        <v>7.9823</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0332</v>
+        <v>7.5428</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.7635</v>
+        <v>0.4398999999999998</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2303000000000003</v>
+        <v>-9.994199999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2166</v>
+        <v>7.492699999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9862999999999996</v>
+        <v>-17.4866</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.6787</v>
+        <v>-4.6309</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5785</v>
+        <v>-0.6643</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.1003</v>
+        <v>-3.9666</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4809</v>
@@ -1078,13 +1078,13 @@
         <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5161</v>
+        <v>0.5639000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5922999999999999</v>
+        <v>0.5064</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.07620000000000005</v>
+        <v>0.05749999999999997</v>
       </c>
       <c r="V8" t="n">
         <v>-3.1056</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>N. LAGARES COUCE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.573399999999999</v>
+        <v>-8.5243</v>
       </c>
       <c r="E9" t="n">
-        <v>5.844399999999999</v>
+        <v>2.433699999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-15.418</v>
+        <v>-10.9577</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.7262</v>
+        <v>-29.0749</v>
       </c>
       <c r="H9" t="n">
-        <v>5.188800000000001</v>
+        <v>-15.6203</v>
       </c>
       <c r="I9" t="n">
-        <v>-8.915100000000001</v>
+        <v>-13.4545</v>
       </c>
       <c r="J9" t="n">
-        <v>13.551</v>
+        <v>8.3513</v>
       </c>
       <c r="K9" t="n">
-        <v>11.0049</v>
+        <v>7.2412</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5459</v>
+        <v>1.1098</v>
       </c>
       <c r="M9" t="n">
-        <v>-17.2773</v>
+        <v>-37.4261</v>
       </c>
       <c r="N9" t="n">
-        <v>-5.8165</v>
+        <v>-22.8617</v>
       </c>
       <c r="O9" t="n">
-        <v>-11.461</v>
+        <v>-14.5643</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7209</v>
+        <v>17.6263</v>
       </c>
       <c r="Q9" t="n">
-        <v>-14.1007</v>
+        <v>-21.9346</v>
       </c>
       <c r="R9" t="n">
-        <v>17.8216</v>
+        <v>39.561</v>
       </c>
       <c r="S9" t="n">
-        <v>10.2022</v>
+        <v>-5.3256</v>
       </c>
       <c r="T9" t="n">
-        <v>8.2319</v>
+        <v>-2.4368</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9701</v>
+        <v>-2.8888</v>
       </c>
       <c r="V9" t="n">
-        <v>-19.7705</v>
+        <v>8.2499</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.8374</v>
+        <v>18.4545</v>
       </c>
       <c r="X9" t="n">
-        <v>-17.933</v>
+        <v>-10.2045</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LATAS CHICO</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.502</v>
+        <v>-8.707000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2490000000000009</v>
+        <v>3.397599999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-10.2528</v>
+        <v>-12.1047</v>
       </c>
       <c r="G10" t="n">
-        <v>-17.0187</v>
+        <v>-4.006200000000002</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.682700000000001</v>
+        <v>-6.502999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-11.3359</v>
+        <v>2.4969</v>
       </c>
       <c r="J10" t="n">
-        <v>10.6723</v>
+        <v>9.8772</v>
       </c>
       <c r="K10" t="n">
-        <v>8.4213</v>
+        <v>0.9539999999999997</v>
       </c>
       <c r="L10" t="n">
-        <v>2.2511</v>
+        <v>8.923299999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-27.691</v>
+        <v>-13.8832</v>
       </c>
       <c r="N10" t="n">
-        <v>-14.1043</v>
+        <v>-7.4569</v>
       </c>
       <c r="O10" t="n">
-        <v>-13.5869</v>
+        <v>-6.4267</v>
       </c>
       <c r="P10" t="n">
-        <v>4.3088</v>
+        <v>0.5874000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-24.2851</v>
+        <v>-13.9052</v>
       </c>
       <c r="R10" t="n">
-        <v>28.5938</v>
+        <v>14.4923</v>
       </c>
       <c r="S10" t="n">
-        <v>5.5285</v>
+        <v>-4.2898</v>
       </c>
       <c r="T10" t="n">
-        <v>7.420999999999999</v>
+        <v>0.8045000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.8926</v>
+        <v>-5.0942</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.3203</v>
+        <v>-0.9986999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>5.9429</v>
+        <v>6.6214</v>
       </c>
       <c r="X10" t="n">
-        <v>-9.263199999999999</v>
+        <v>-7.619999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>A. ESPIÑEIRA ANDRADE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.374</v>
+        <v>-11.9473</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7734000000000001</v>
+        <v>9.4885</v>
       </c>
       <c r="F11" t="n">
-        <v>-14.1473</v>
+        <v>-21.4358</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.006200000000002</v>
+        <v>-15.6195</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.502999999999999</v>
+        <v>-4.201099999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4969</v>
+        <v>-11.4187</v>
       </c>
       <c r="J11" t="n">
-        <v>9.8772</v>
+        <v>15.2758</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9539999999999997</v>
+        <v>8.131499999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>8.923299999999999</v>
+        <v>7.1442</v>
       </c>
       <c r="M11" t="n">
-        <v>-13.8832</v>
+        <v>-30.895</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.4569</v>
+        <v>-12.3328</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.4267</v>
+        <v>-18.5627</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5874000000000001</v>
+        <v>11.1631</v>
       </c>
       <c r="Q11" t="n">
-        <v>-13.9052</v>
+        <v>-10.5755</v>
       </c>
       <c r="R11" t="n">
-        <v>14.4923</v>
+        <v>21.7386</v>
       </c>
       <c r="S11" t="n">
-        <v>-8.956799999999999</v>
+        <v>-4.1727</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.8197</v>
+        <v>-1.7297</v>
       </c>
       <c r="U11" t="n">
-        <v>-7.1372</v>
+        <v>-2.4428</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9986999999999999</v>
+        <v>-3.3183</v>
       </c>
       <c r="W11" t="n">
-        <v>6.6214</v>
+        <v>6.5187</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.619999999999999</v>
+        <v>-9.8371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. GOMEZ LLANES</t>
+          <t>M. LATAS CHICO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.7743</v>
+        <v>-13.1254</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.2896</v>
+        <v>-3.0257</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4848</v>
+        <v>-10.0996</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.669500000000001</v>
+        <v>-17.0187</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4829</v>
+        <v>-5.682700000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-7.186500000000001</v>
+        <v>-11.3359</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2705000000000002</v>
+        <v>10.6723</v>
       </c>
       <c r="K12" t="n">
-        <v>2.190700000000001</v>
+        <v>8.4213</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.4613</v>
+        <v>2.2511</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.3988</v>
+        <v>-27.691</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.6737</v>
+        <v>-14.1043</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.7252</v>
+        <v>-13.5869</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.8755</v>
+        <v>4.3088</v>
       </c>
       <c r="Q12" t="n">
-        <v>-18.6056</v>
+        <v>-24.2851</v>
       </c>
       <c r="R12" t="n">
-        <v>12.7301</v>
+        <v>28.5938</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9899</v>
+        <v>2.905</v>
       </c>
       <c r="T12" t="n">
-        <v>1.659</v>
+        <v>4.6443</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6691999999999999</v>
+        <v>-1.7391</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.2195</v>
+        <v>-3.3203</v>
       </c>
       <c r="W12" t="n">
-        <v>1.9275</v>
+        <v>5.9429</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.147</v>
+        <v>-9.263199999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. ESPIÑEIRA ANDRADE</t>
+          <t>J. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.0517</v>
+        <v>-15.4822</v>
       </c>
       <c r="E13" t="n">
-        <v>6.293299999999999</v>
+        <v>-11.5894</v>
       </c>
       <c r="F13" t="n">
-        <v>-23.3445</v>
+        <v>-3.893</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.6195</v>
+        <v>-18.6925</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.201099999999999</v>
+        <v>-5.875</v>
       </c>
       <c r="I13" t="n">
-        <v>-11.4187</v>
+        <v>-12.8171</v>
       </c>
       <c r="J13" t="n">
-        <v>15.2758</v>
+        <v>0.2657000000000007</v>
       </c>
       <c r="K13" t="n">
-        <v>8.131499999999999</v>
+        <v>1.9899</v>
       </c>
       <c r="L13" t="n">
-        <v>7.1442</v>
+        <v>-1.7239</v>
       </c>
       <c r="M13" t="n">
-        <v>-30.895</v>
+        <v>-18.9581</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.3328</v>
+        <v>-7.8655</v>
       </c>
       <c r="O13" t="n">
-        <v>-18.5627</v>
+        <v>-11.0932</v>
       </c>
       <c r="P13" t="n">
-        <v>11.1631</v>
+        <v>-4.5045</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.5755</v>
+        <v>-26.0473</v>
       </c>
       <c r="R13" t="n">
-        <v>21.7386</v>
+        <v>21.5428</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.2773</v>
+        <v>0.2098</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.925</v>
+        <v>0.2847999999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.3518</v>
+        <v>-0.0744999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.3183</v>
+        <v>7.5051</v>
       </c>
       <c r="W13" t="n">
-        <v>6.5187</v>
+        <v>13.9086</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.8371</v>
+        <v>-6.403499999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. LAGARES COUCE</t>
+          <t>A. GOMEZ LLANES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.6024</v>
+        <v>-16.4774</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.1584</v>
+        <v>-15.7254</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.4441</v>
+        <v>-0.7518000000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>-29.0749</v>
+        <v>-9.669500000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-15.6203</v>
+        <v>-2.4829</v>
       </c>
       <c r="I14" t="n">
-        <v>-13.4545</v>
+        <v>-7.186500000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>8.3513</v>
+        <v>-0.2705000000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>7.2412</v>
+        <v>2.190700000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1098</v>
+        <v>-2.4613</v>
       </c>
       <c r="M14" t="n">
-        <v>-37.4261</v>
+        <v>-9.3988</v>
       </c>
       <c r="N14" t="n">
-        <v>-22.8617</v>
+        <v>-4.6737</v>
       </c>
       <c r="O14" t="n">
-        <v>-14.5643</v>
+        <v>-4.7252</v>
       </c>
       <c r="P14" t="n">
-        <v>17.6263</v>
+        <v>-5.8755</v>
       </c>
       <c r="Q14" t="n">
-        <v>-21.9346</v>
+        <v>-18.6056</v>
       </c>
       <c r="R14" t="n">
-        <v>39.561</v>
+        <v>12.7301</v>
       </c>
       <c r="S14" t="n">
-        <v>-15.4038</v>
+        <v>1.287</v>
       </c>
       <c r="T14" t="n">
-        <v>-8.0288</v>
+        <v>1.2231</v>
       </c>
       <c r="U14" t="n">
-        <v>-7.3751</v>
+        <v>0.06380000000000002</v>
       </c>
       <c r="V14" t="n">
-        <v>8.2499</v>
+        <v>-2.2195</v>
       </c>
       <c r="W14" t="n">
-        <v>18.4545</v>
+        <v>1.9275</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.2045</v>
+        <v>-4.147</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GONZALEZ VAZQUEZ</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-19.9004</v>
+        <v>-16.8978</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.9298</v>
+        <v>0.2224000000000006</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.970600000000001</v>
+        <v>-17.1205</v>
       </c>
       <c r="G15" t="n">
-        <v>-18.6925</v>
+        <v>-3.7262</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.875</v>
+        <v>5.188800000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-12.8171</v>
+        <v>-8.915100000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2657000000000007</v>
+        <v>13.551</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9899</v>
+        <v>11.0049</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.7239</v>
+        <v>2.5459</v>
       </c>
       <c r="M15" t="n">
-        <v>-18.9581</v>
+        <v>-17.2773</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.8655</v>
+        <v>-5.8165</v>
       </c>
       <c r="O15" t="n">
-        <v>-11.0932</v>
+        <v>-11.461</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.5045</v>
+        <v>3.7209</v>
       </c>
       <c r="Q15" t="n">
-        <v>-26.0473</v>
+        <v>-14.1007</v>
       </c>
       <c r="R15" t="n">
-        <v>21.5428</v>
+        <v>17.8216</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.2085</v>
+        <v>2.8775</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.056</v>
+        <v>2.6101</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1523</v>
+        <v>0.2676000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5051</v>
+        <v>-19.7705</v>
       </c>
       <c r="W15" t="n">
-        <v>13.9086</v>
+        <v>-1.8374</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.403499999999999</v>
+        <v>-17.933</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-32.6762</v>
+        <v>-16.9625</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.2545</v>
+        <v>-3.150100000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-20.4216</v>
+        <v>-13.8124</v>
       </c>
       <c r="G16" t="n">
         <v>-30.4128</v>
@@ -1702,13 +1702,13 @@
         <v>51.8998</v>
       </c>
       <c r="S16" t="n">
-        <v>-19.9791</v>
+        <v>-4.265400000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-7.6924</v>
+        <v>1.4119</v>
       </c>
       <c r="U16" t="n">
-        <v>-12.2866</v>
+        <v>-5.6776</v>
       </c>
       <c r="V16" t="n">
         <v>10.4695</v>
@@ -1735,13 +1735,13 @@
         <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>-37.8927</v>
+        <v>-33.5907</v>
       </c>
       <c r="E17" t="n">
-        <v>-25.6523</v>
+        <v>-22.6025</v>
       </c>
       <c r="F17" t="n">
-        <v>-12.2402</v>
+        <v>-10.9883</v>
       </c>
       <c r="G17" t="n">
         <v>-31.5633</v>
@@ -1780,13 +1780,13 @@
         <v>28.5936</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.0698</v>
+        <v>0.2321</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.5641</v>
+        <v>1.4862</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.5059</v>
+        <v>-1.2543</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6930999999999997</v>
@@ -1813,19 +1813,19 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-64.52359999999999</v>
+        <v>-42.94759999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>83.5746</v>
+        <v>92.18769999999995</v>
       </c>
       <c r="F18" t="n">
-        <v>-148.097</v>
+        <v>-135.1356</v>
       </c>
       <c r="G18" t="n">
         <v>-108.0187</v>
       </c>
       <c r="H18" t="n">
-        <v>16.93129999999999</v>
+        <v>16.9313</v>
       </c>
       <c r="I18" t="n">
         <v>-124.9504</v>
@@ -1837,7 +1837,7 @@
         <v>210.3954</v>
       </c>
       <c r="L18" t="n">
-        <v>68.1275</v>
+        <v>68.12749999999998</v>
       </c>
       <c r="M18" t="n">
         <v>-386.5425</v>
@@ -1858,16 +1858,16 @@
         <v>427.9249</v>
       </c>
       <c r="S18" t="n">
-        <v>-8.878499999999995</v>
+        <v>12.6975</v>
       </c>
       <c r="T18" t="n">
-        <v>27.0609</v>
+        <v>35.6747</v>
       </c>
       <c r="U18" t="n">
-        <v>-35.9388</v>
+        <v>-22.9762</v>
       </c>
       <c r="V18" t="n">
-        <v>39.6428</v>
+        <v>39.64279999999999</v>
       </c>
       <c r="W18" t="n">
         <v>193.191</v>
